--- a/public/templates/Customer_sample_template.xlsx
+++ b/public/templates/Customer_sample_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>Customer Name</t>
   </si>
@@ -108,12 +108,6 @@
   </si>
   <si>
     <t>GSTIN No.</t>
-  </si>
-  <si>
-    <t>GST Registered Name</t>
-  </si>
-  <si>
-    <t>GSTIN Reg. Date</t>
   </si>
   <si>
     <t>TDS Applicable</t>
@@ -899,13 +893,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1186,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
@@ -1204,16 +1191,15 @@
     <col min="19" max="25" width="9.14166666666667" style="2"/>
     <col min="26" max="26" width="11.2833333333333" style="2" customWidth="1"/>
     <col min="27" max="27" width="9.14166666666667" style="2"/>
-    <col min="28" max="28" width="15.5666666666667" style="2" customWidth="1"/>
+    <col min="28" max="28" width="11.425" style="2" customWidth="1"/>
     <col min="29" max="29" width="9.14166666666667" style="2"/>
-    <col min="30" max="30" width="11.425" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9.14166666666667" style="2"/>
-    <col min="32" max="32" width="14.1416666666667" style="2" customWidth="1"/>
-    <col min="33" max="36" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="9.14166666666667" style="2"/>
+    <col min="30" max="30" width="14.1416666666667" style="2" customWidth="1"/>
+    <col min="31" max="34" width="10.8583333333333" style="2" customWidth="1"/>
+    <col min="35" max="16383" width="9.14166666666667" style="2"/>
+    <col min="16384" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:36">
+    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:34">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1316,29 +1302,23 @@
       <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="2" ht="99.75" spans="1:36">
+    <row r="2" ht="99.75" spans="1:34">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1350,7 +1330,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1360,34 +1340,32 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
       <c r="AD2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AG2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:34">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1422,10 +1400,8 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:34">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1460,10 +1436,8 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="7"/>
       <c r="AH4" s="7"/>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="7"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:34">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1498,10 +1472,8 @@
       <c r="AF5" s="7"/>
       <c r="AG5" s="7"/>
       <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:34">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1536,10 +1508,8 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="7"/>
       <c r="AH6" s="7"/>
-      <c r="AI6" s="7"/>
-      <c r="AJ6" s="7"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:34">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1574,10 +1544,8 @@
       <c r="AF7" s="7"/>
       <c r="AG7" s="7"/>
       <c r="AH7" s="7"/>
-      <c r="AI7" s="7"/>
-      <c r="AJ7" s="7"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:34">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1612,10 +1580,8 @@
       <c r="AF8" s="7"/>
       <c r="AG8" s="7"/>
       <c r="AH8" s="7"/>
-      <c r="AI8" s="7"/>
-      <c r="AJ8" s="7"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:34">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1650,10 +1616,8 @@
       <c r="AF9" s="7"/>
       <c r="AG9" s="7"/>
       <c r="AH9" s="7"/>
-      <c r="AI9" s="7"/>
-      <c r="AJ9" s="7"/>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:34">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1688,8 +1652,6 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
-      <c r="AI10" s="7"/>
-      <c r="AJ10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
